--- a/product-import-template.xlsx
+++ b/product-import-template.xlsx
@@ -49,49 +49,56 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>How many you can sell before the website shows it as sold out. Each order takes one off. Leave blank for 10.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <t>The flower the arrangement is mostly made of.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <t>What a customer would call it when filtering. Use mixed for genuinely multi-coloured.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <t>Number of stems or heads, if it is a number worth quoting.</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <t>Two or three sentences. What it is, what is in it, who it suits.</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <t>Paste the photo into this cell (Insert &gt; Picture, then drag it over the cell). One per product.</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <t>Instead of pasting: put the photo in the same folder as this file and type its file name here, e.g. red-roses.jpg</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <t>Yes puts it on the website immediately. No saves it as a draft for you to check first.</t>
@@ -110,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>Product name *</t>
   </si>
@@ -124,6 +131,9 @@
     <t>Was price QAR</t>
   </si>
   <si>
+    <t>Stock</t>
+  </si>
+  <si>
     <t>Category 1 *</t>
   </si>
   <si>
@@ -353,6 +363,9 @@
   </si>
   <si>
     <t>If a product comes in more than one size, use one row per size and give every row the SAME product name. Put Small / Medium / Large, or 50 / 100 / 200, in the Size column, each with its own price. They become one product page with a size chooser.</t>
+  </si>
+  <si>
+    <t>How many of each flower you can sell. Every order takes one off, and at 0 the website shows it as sold out until you add more — in the admin, or by importing this sheet again with a new number. Leave it blank and a new flower starts at 10. On a flower that already exists, a blank cell leaves its stock as it is.</t>
   </si>
   <si>
     <t>Prices</t>
@@ -835,23 +848,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:O401"/>
   <sheetFormatPr defaultRowHeight="84" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="2" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" customWidth="1"/>
-    <col min="5" max="7" width="22" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2" customWidth="1"/>
-    <col min="11" max="11" width="52" style="1" customWidth="1"/>
-    <col min="12" max="13" width="24" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2" customWidth="1"/>
+    <col min="6" max="8" width="22" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="2" customWidth="1"/>
+    <col min="12" max="12" width="52" style="1" customWidth="1"/>
+    <col min="13" max="14" width="24" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -864,7 +878,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -879,10 +893,10 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -894,465 +908,471 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="7">
         <v>450</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>15</v>
+      <c r="E2" s="7">
+        <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="7">
         <v>50</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="266" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="267" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="270" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="273" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="274" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="275" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="276" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="289" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="291" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="292" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="293" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="294" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="295" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="296" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="301" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="303" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="305" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="308" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="309" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="310" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="311" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="312" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="313" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="314" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="315" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="316" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="317" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="320" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="321" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="322" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="323" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="324" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="325" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="326" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="327" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="328" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="329" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="330" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="331" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="332" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="333" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="334" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="335" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="336" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="337" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="338" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="339" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="340" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="342" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="343" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="344" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="345" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="346" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="347" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="348" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="349" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="350" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="352" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="353" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="354" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="355" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="356" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="357" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="358" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="359" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="360" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="361" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="362" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="363" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="364" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="365" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="366" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="367" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="368" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="369" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="370" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="371" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="372" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="373" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="374" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="375" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="376" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="377" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="378" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="379" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="380" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="381" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="382" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="383" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="384" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="386" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="387" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="388" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="389" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="390" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="391" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="392" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="393" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="394" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="395" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="396" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="397" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="398" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="399" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="400" spans="5:14" x14ac:dyDescent="0.25"/>
-    <row r="401" spans="5:14" x14ac:dyDescent="0.25"/>
+      <c r="O2" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="6:15" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="6:15" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="E10:E401">
+    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="F10:F401">
       <formula1>Lists!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="E2:E401">
+    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="F2:F401">
       <formula1>Lists!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="F10:G401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="G10:H401">
       <formula1>Lists!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="F2:G401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="G2:H401">
       <formula1>Lists!$A$2:$A$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="H10:H401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="I10:I401">
       <formula1>Lists!$B$2:$B$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="H2:H401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="I2:I401">
       <formula1>Lists!$B$2:$B$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="I10:I401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="J10:J401">
       <formula1>Lists!$C$2:$C$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="I2:I401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="J2:J401">
       <formula1>Lists!$C$2:$C$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="N10:N401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="O10:O401">
       <formula1>Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="N2:N401">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Pick from the list" error="Use one of the values in the dropdown. If something is genuinely missing, ask for it to be added rather than typing it here." sqref="O2:O401">
       <formula1>Lists!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -1369,244 +1389,244 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1617,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="104" style="8" customWidth="1"/>
@@ -1625,55 +1645,55 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="51" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" ht="51" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>82</v>
       </c>
@@ -1683,7 +1703,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>84</v>
       </c>
@@ -1693,18 +1713,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" ht="66" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" ht="51" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="16" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+    <row r="17" ht="66" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1714,23 +1734,33 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="21" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/product-import-template.xlsx
+++ b/product-import-template.xlsx
@@ -45,7 +45,7 @@
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>Only for a Hot Deal: the old price, shown struck through. Leave blank otherwise.</t>
+          <t>Only for an offer: the old price, shown struck through. Leave blank otherwise.</t>
         </r>
       </text>
     </comment>
@@ -191,7 +191,7 @@
     <t>Publish</t>
   </si>
   <si>
-    <t>Hot Deal</t>
+    <t>Offers</t>
   </si>
   <si>
     <t>Hand-Tied Bouquets</t>
@@ -371,7 +371,7 @@
     <t>Prices</t>
   </si>
   <si>
-    <t>Plain numbers in Qatari riyal: 450, not 450 QAR and not 45000. Was price QAR is only for a Hot Deal — fill it in and the old price appears struck through beside the new one.</t>
+    <t>Plain numbers in Qatari riyal: 450, not 450 QAR and not 45000. Was price QAR is only for an offer — fill it in and the old price appears struck through beside the new one.</t>
   </si>
   <si>
     <t>Categories</t>
